--- a/Documentation/classes_inscription/class_Level.xlsx
+++ b/Documentation/classes_inscription/class_Level.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\classes_inscription\classes_inscription\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AeroData\main_for_all\python\MathUp\Documentation\classes_inscription\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E81FE13-B5AD-4D88-BA43-19E33AEE02D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A81BCD4-C84A-4EC1-A2D7-1364E366C1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>תכונות(שדות)</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>מעדכנת את כל המשתנים, בודקת תשובות של שחקן ובסופה מציירת את כל העצמים על המסך.</t>
+  </si>
+  <si>
+    <t>wrong_answers</t>
+  </si>
+  <si>
+    <t>רשימה של כל התשובות לא נכונות.</t>
   </si>
 </sst>
 </file>
@@ -374,13 +380,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -403,12 +408,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -686,33 +694,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7265625" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,7 +734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -736,71 +744,71 @@
       <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -810,49 +818,49 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -862,67 +870,67 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
@@ -932,7 +940,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -942,48 +950,60 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="6"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="13"/>
+      <c r="B27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
